--- a/data/trans_orig/IP07_C12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C12_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de cansancio para realizar lo que le gusta en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de haber estado demasiado cansado/a para disfrutar de las cosas que le gusta hacer, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4870</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1601</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9568</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1698</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5331</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6067</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4478</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10166</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>874</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22858</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>28201</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>37818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75394</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67120</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82778</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51431</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>45346</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>57112</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>76436</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67535</t>
+          <t>47317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>59437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>127867</t>
+          <t>129796</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116575</t>
+          <t>118149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136464</t>
+          <t>139175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3867</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5558</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>824</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32479</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21261</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48813</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>46242</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21094</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>90006</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32,44%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>63,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>16036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>79322</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>42958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140390</t>
+          <t>75300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136166</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>119439</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>147405</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>93322</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>50740</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>117709</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>136883</t>
+          <t>99665</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119960</t>
+          <t>89519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148905</t>
+          <t>106747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>230204</t>
+          <t>235831</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170763</t>
+          <t>217678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258148</t>
+          <t>249407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>363</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4765</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>47686</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>34801</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>65589</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>58708</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>32701</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>113487</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>53,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>106734</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78553</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178588</t>
+          <t>105456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>211560</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>192651</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>225060</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>71,33%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>144753</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>93502</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>170004</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>68,78%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>44,42%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>80,77%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>213317</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191787</t>
+          <t>143121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227517</t>
+          <t>164608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>358070</t>
+          <t>365627</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>288306</t>
+          <t>343993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385157</t>
+          <t>384197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>577</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
